--- a/data/trans_bre/IP16B02-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP16B02-Edad-trans_bre.xlsx
@@ -639,12 +639,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 16,24</t>
+          <t>-7,88; 16,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,3</t>
+          <t>0,0; 29,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -654,12 +654,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 19,54</t>
+          <t>-7,97; 19,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,99</t>
+          <t>0,0; 41,35</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-40,54; -1,89</t>
+          <t>-41,11; -3,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-24,93; 15,21</t>
+          <t>-25,58; 15,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-36,17; -4,01</t>
+          <t>-36,26; -3,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-42,22; -2,02</t>
+          <t>-42,98; -3,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-28,78; 21,35</t>
+          <t>-29,83; 22,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-36,95; -4,6</t>
+          <t>-37,52; -4,35</t>
         </is>
       </c>
     </row>
@@ -799,12 +799,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-32,42; 11,18</t>
+          <t>-31,83; 12,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 30,67</t>
+          <t>-7,26; 30,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -814,12 +814,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-34,51; 13,35</t>
+          <t>-33,8; 14,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 45,66</t>
+          <t>-7,64; 44,39</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-33,76; 28,16</t>
+          <t>-31,69; 28,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-46,82; -5,13</t>
+          <t>-47,51; -7,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-39,2; 6,87</t>
+          <t>-39,28; 6,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-43,75; 54,55</t>
+          <t>-41,36; 56,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-49,48; -7,26</t>
+          <t>-49,43; -9,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-41,62; 7,1</t>
+          <t>-41,02; 6,03</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-21,3; 3,06</t>
+          <t>-21,95; 2,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-17,15; 2,94</t>
+          <t>-16,6; 3,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,91; 1,57</t>
+          <t>-17,29; 2,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-23,69; 3,62</t>
+          <t>-24,49; 2,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,73; 3,24</t>
+          <t>-18,43; 3,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,71; 1,78</t>
+          <t>-18,78; 3,19</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16B02-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP16B02-Edad-trans_bre.xlsx
@@ -639,12 +639,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 16,2</t>
+          <t>-10,04; 16,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,27</t>
+          <t>0,0; 30,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -654,12 +654,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 19,88</t>
+          <t>-10,12; 19,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,35</t>
+          <t>0,0; 44,37</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-41,11; -3,08</t>
+          <t>-40,92; -2,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-25,58; 15,9</t>
+          <t>-25,72; 14,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-36,26; -3,69</t>
+          <t>-35,73; -4,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-42,98; -3,63</t>
+          <t>-42,41; -3,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-29,83; 22,75</t>
+          <t>-29,44; 19,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-37,52; -4,35</t>
+          <t>-37,22; -5,25</t>
         </is>
       </c>
     </row>
@@ -799,12 +799,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-31,83; 12,31</t>
+          <t>-29,33; 12,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 30,32</t>
+          <t>-9,52; 29,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -814,12 +814,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-33,8; 14,69</t>
+          <t>-31,02; 14,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 44,39</t>
+          <t>-10,48; 44,6</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-31,69; 28,46</t>
+          <t>-29,9; 28,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-47,51; -7,67</t>
+          <t>-49,69; -9,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-39,28; 6,52</t>
+          <t>-37,3; 4,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-41,36; 56,91</t>
+          <t>-39,92; 57,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-49,43; -9,96</t>
+          <t>-52,08; -11,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-41,02; 6,03</t>
+          <t>-39,24; 4,48</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-21,95; 2,46</t>
+          <t>-21,51; 2,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,6; 3,08</t>
+          <t>-16,78; 2,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,29; 2,8</t>
+          <t>-17,94; 2,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-24,49; 2,94</t>
+          <t>-23,73; 2,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,43; 3,31</t>
+          <t>-18,46; 2,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,78; 3,19</t>
+          <t>-19,2; 2,48</t>
         </is>
       </c>
     </row>
